--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -525,8 +525,7 @@
 </t>
   </si>
   <si>
-    <t>実施されるプラン、提案、依頼  
-【JP Core仕様】未使用</t>
+    <t>実施されるプラン、提案、依頼  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>本プロファイル（特定の歯の有無・状態）は口腔診査レポートに紐付く前提のため、本プロファイル特有の定義はしない。</t>
@@ -555,8 +554,7 @@
 </t>
   </si>
   <si>
-    <t>参照されるイベントの一部分  
-【JP Core仕様】未使用</t>
+    <t>参照されるイベントの一部分 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
@@ -574,8 +572,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態  
-【JP Core仕様】ステータス</t>
+    <t>結果の状態 【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -618,16 +615,15 @@
 </t>
   </si>
   <si>
-    <t>Observationの種類（タイプ）の分類
-【JP Core仕様】以下を指定する。
+    <t>Observationの種類（タイプ）の分類</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】以下を指定する。
 第1コード：exam
 第2コード：LP89803-8 （Dental）
 第3コード：DO-1-03 （MissingToothCondition）</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
-  </si>
-  <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
@@ -919,6 +915,9 @@
   </si>
   <si>
     <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -5574,7 +5573,7 @@
         <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>194</v>
@@ -5661,7 +5660,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5779,7 +5778,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5899,7 +5898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6021,7 +6020,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6139,7 +6138,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6259,7 +6258,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6304,7 +6303,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6381,7 +6380,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>244</v>
@@ -6501,7 +6500,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>252</v>
@@ -6544,7 +6543,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6621,7 +6620,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6741,7 +6740,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6863,7 +6862,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6985,13 +6984,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7016,13 +7015,13 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>194</v>
@@ -7054,7 +7053,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7107,7 +7106,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>207</v>
@@ -7225,7 +7224,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>214</v>
@@ -7345,7 +7344,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>220</v>
@@ -7467,7 +7466,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>230</v>
@@ -7585,7 +7584,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>232</v>
@@ -7705,7 +7704,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>234</v>
@@ -7750,7 +7749,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7827,7 +7826,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>244</v>
@@ -7947,7 +7946,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>252</v>
@@ -7990,7 +7989,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8067,7 +8066,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8187,7 +8186,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8309,7 +8308,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8431,14 +8430,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8460,16 +8459,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8494,13 +8493,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8518,7 +8517,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8533,30 +8532,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8671,10 +8670,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8791,10 +8790,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,10 +8819,10 @@
         <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>224</v>
@@ -8913,10 +8912,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9031,10 +9030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9151,10 +9150,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9196,7 +9195,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9273,10 +9272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9393,10 +9392,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9436,7 +9435,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9513,10 +9512,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9559,7 +9558,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9633,10 +9632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9755,10 +9754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9877,10 +9876,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9903,19 +9902,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9964,7 +9963,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9979,19 +9978,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9999,10 +9998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10025,16 +10024,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10084,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10105,13 +10104,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10119,14 +10118,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10145,19 +10144,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10206,7 +10205,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10221,19 +10220,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10241,14 +10240,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10267,19 +10266,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10328,7 +10327,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10343,19 +10342,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10363,10 +10362,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10389,16 +10388,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10448,7 +10447,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10469,13 +10468,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10483,10 +10482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10509,19 +10508,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10570,7 +10569,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10585,19 +10584,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10605,10 +10604,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10634,16 +10633,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10692,7 +10691,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10701,7 +10700,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10710,27 +10709,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10756,16 +10755,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10790,13 +10789,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10814,7 +10813,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10822,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10838,7 +10837,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10849,14 +10848,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10878,16 +10877,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10912,13 +10911,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10936,7 +10935,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10954,27 +10953,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10997,19 +10996,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11058,7 +11057,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11079,10 +11078,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11093,10 +11092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11122,13 +11121,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11158,7 +11157,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11176,7 +11175,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11194,27 +11193,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11329,10 +11328,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11449,13 +11448,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11477,13 +11476,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11569,13 +11568,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11597,13 +11596,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11689,10 +11688,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11811,10 +11810,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11933,10 +11932,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11962,16 +11961,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11996,13 +11995,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12020,7 +12019,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12041,10 +12040,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12055,10 +12054,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12081,16 +12080,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12140,7 +12139,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12158,27 +12157,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12201,16 +12200,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12260,7 +12259,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12278,27 +12277,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12321,19 +12320,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12382,7 +12381,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12394,7 +12393,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12403,10 +12402,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12417,10 +12416,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12535,10 +12534,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12655,14 +12654,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12684,10 +12683,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12742,7 +12741,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12777,10 +12776,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12803,13 +12802,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12860,7 +12859,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12869,7 +12868,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12881,10 +12880,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12895,10 +12894,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12921,13 +12920,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12978,7 +12977,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12987,7 +12986,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12999,10 +12998,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13013,10 +13012,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13042,16 +13041,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13079,10 +13078,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13100,7 +13099,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13118,13 +13117,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13135,10 +13134,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13164,16 +13163,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13198,13 +13197,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13222,7 +13221,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13240,13 +13239,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13257,10 +13256,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13283,17 +13282,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13342,7 +13341,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13366,7 +13365,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13377,10 +13376,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13406,10 +13405,10 @@
         <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13460,7 +13459,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13481,10 +13480,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13495,10 +13494,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13509,7 +13508,7 @@
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13521,16 +13520,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13580,7 +13579,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13601,10 +13600,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13615,10 +13614,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13641,16 +13640,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13700,7 +13699,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13721,10 +13720,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13735,10 +13734,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13761,19 +13760,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13822,7 +13821,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13843,10 +13842,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13857,10 +13856,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13975,10 +13974,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14095,14 +14094,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14124,10 +14123,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14182,7 +14181,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14217,10 +14216,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14246,16 +14245,16 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14280,13 +14279,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14304,7 +14303,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14322,16 +14321,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14339,10 +14338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14457,10 +14456,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14577,10 +14576,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14652,7 +14651,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14697,10 +14696,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14815,10 +14814,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14935,10 +14934,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15057,10 +15056,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15177,10 +15176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15297,10 +15296,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15417,10 +15416,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15539,13 +15538,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15570,10 +15569,10 @@
         <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>224</v>
@@ -15608,7 +15607,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15661,10 +15660,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15779,10 +15778,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15899,10 +15898,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15944,7 +15943,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16021,10 +16020,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16141,10 +16140,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16261,10 +16260,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16381,10 +16380,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16503,13 +16502,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16534,10 +16533,10 @@
         <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>224</v>
@@ -16572,7 +16571,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16625,10 +16624,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16743,10 +16742,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16863,10 +16862,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16908,7 +16907,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16985,10 +16984,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17105,10 +17104,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17225,10 +17224,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17345,10 +17344,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17467,10 +17466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17589,10 +17588,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17615,19 +17614,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17676,7 +17675,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17694,27 +17693,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17740,16 +17739,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17774,13 +17773,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -17798,7 +17797,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17807,7 +17806,7 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17822,7 +17821,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17833,14 +17832,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17862,16 +17861,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17896,13 +17895,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17920,7 +17919,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17938,27 +17937,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17984,16 +17983,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18042,7 +18041,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18063,10 +18062,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
